--- a/testdata/data/Book1.xlsx
+++ b/testdata/data/Book1.xlsx
@@ -3,13 +3,8 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="153222"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tec Data\eclipse-workspace\vizza_insurence\testdata\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="16340" windowHeight="3170" firstSheet="2" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16140" windowHeight="3130" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="VEHICLE" sheetId="1" r:id="rId1"/>
@@ -18,6 +13,7 @@
     <sheet name="NewIndaia" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
+  <oleSize ref="A1:I9"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
